--- a/outputs/cream/novus/primary_chain_output.xlsx
+++ b/outputs/cream/novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.166352131060911e-05</v>
+        <v>3.166352131058586e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1.807358615624225e-13</v>
+        <v>1.807358615622328e-13</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.250471045105603e-20</v>
+        <v>2.250471045106072e-20</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.604635633535988e-13</v>
+        <v>3.604635633536289e-13</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.169300175083072e-11</v>
+        <v>1.169300175082499e-11</v>
       </c>
       <c r="G3" t="n">
         <v>0.09309066682789993</v>
@@ -929,19 +929,19 @@
         <v>3.793680252396324</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3345340871189739</v>
+        <v>0.3345340871189721</v>
       </c>
       <c r="L2" t="n">
         <v>-1.002572700947699</v>
       </c>
       <c r="M2" t="n">
-        <v>2.775901445899018e-16</v>
+        <v>2.775901445894396e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07891071636138866</v>
+        <v>0.07891071636138901</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3144592712848959</v>
+        <v>0.3144592712849068</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.889712370853929</v>
+        <v>0.8897123708539287</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2018078467373643</v>
+        <v>0.20180784673736</v>
       </c>
       <c r="G2" t="n">
-        <v>1.393192716168525e-262</v>
+        <v>1.393192716168049e-262</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -57021,10 +57021,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.905619429434132</v>
+        <v>2.905619429434134</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8880608229621922</v>
+        <v>-0.8880608229621898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57037,10 +57037,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3.166679443444792</v>
+        <v>3.166679443444793</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9678500646420563</v>
+        <v>-0.9678500646420531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>3.190134796965924</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.9750188563770777</v>
+        <v>-0.9750188563770745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57069,10 +57069,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.192242180629738</v>
+        <v>3.192242180629739</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9756629479094464</v>
+        <v>-0.9756629479094431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>3.192431521877676</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9757208173409214</v>
+        <v>-0.9757208173409182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>3.192448533544221</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9757260167123321</v>
+        <v>-0.9757260167123288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>3.192450061984546</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.975726483858153</v>
+        <v>-0.9757264838581496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57133,10 +57133,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.192450199309706</v>
+        <v>3.192450199309707</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9757265258296146</v>
+        <v>-0.9757265258296113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57149,10 +57149,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.192450211647904</v>
+        <v>3.192450211647905</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9757265296006076</v>
+        <v>-0.9757265296006042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57165,10 +57165,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.192450212756449</v>
+        <v>3.19245021275645</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.9757265299394184</v>
+        <v>-0.9757265299394151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57181,10 +57181,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.192450212856048</v>
+        <v>3.192450212856049</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.9757265299698594</v>
+        <v>-0.9757265299698561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>3.192450212864997</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.9757265299725945</v>
+        <v>-0.9757265299725911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57216,7 +57216,7 @@
         <v>3.192450212865801</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.9757265299728402</v>
+        <v>-0.9757265299728368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>3.192450212865873</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.9757265299728622</v>
+        <v>-0.9757265299728589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.9757265299728642</v>
+        <v>-0.9757265299728609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57264,7 +57264,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.9757265299728644</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>3.19245021286588</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.9757265299728645</v>
+        <v>-0.9757265299728611</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
